--- a/V2 BETA/V2 Shared Files/valkyris v2 control boards.xlsx
+++ b/V2 BETA/V2 Shared Files/valkyris v2 control boards.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -17,7 +17,23 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -27,9 +43,138 @@
     <t xml:space="preserve">compatabile control boards with  RRF  3.7 </t>
   </si>
   <si>
+    <t>valkyrie  v2</t>
+  </si>
+  <si>
     <t>STM32H7</t>
   </si>
   <si>
+    <t xml:space="preserve">PWM o/p Fans /SSR 1A </t>
+  </si>
+  <si>
+    <t>12v PWM &gt;2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inputs </t>
+  </si>
+  <si>
+    <t>Hot end Heater</t>
+  </si>
+  <si>
+    <t>output 12V 2A</t>
+  </si>
+  <si>
+    <t>Output Digital</t>
+  </si>
+  <si>
+    <t>Humidity Sensor BME28</t>
+  </si>
+  <si>
+    <t>PT100/1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thermisistors </t>
+  </si>
+  <si>
+    <t>steppers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12V supply </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V supply </t>
+  </si>
+  <si>
+    <t>wifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ethernet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost $ with stepper drives </t>
+  </si>
+  <si>
+    <t>cost $ no drivers</t>
+  </si>
+  <si>
+    <t>drivers ea</t>
+  </si>
+  <si>
+    <t>Requireed for V2</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Fly-ProX10 H723</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>6(2wire)2(4 wire)</t>
+  </si>
+  <si>
+    <t>1(bedout)</t>
+  </si>
+  <si>
+    <t>Fly-Super8Pro H743</t>
+  </si>
+  <si>
+    <t>no stock</t>
+  </si>
+  <si>
+    <t>Fly-Super8Pro H723</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>10 (5,12,24v indipendant )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4(5A each) </t>
+  </si>
+  <si>
+    <t>1option $13</t>
+  </si>
+  <si>
+    <t>1option$15 (E&amp;W)</t>
+  </si>
+  <si>
+    <t>TMC2240 $8</t>
+  </si>
+  <si>
+    <t>BTT Kraken H723</t>
+  </si>
+  <si>
+    <t>6(2wire)2(4 wire) (5,12,24v indipendant )</t>
+  </si>
+  <si>
+    <t>4(6A)</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>$111(tmc2160)</t>
+  </si>
+  <si>
+    <t>BTT Octopus Pro v1.1 H723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spoke to BTT no stock for a few weeks </t>
+  </si>
+  <si>
+    <t>BTT Scylla v1.0 H723</t>
+  </si>
+  <si>
+    <t>$88 (TMC2160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruled out </t>
+  </si>
+  <si>
     <t>AFC-Lite V1.0</t>
   </si>
   <si>
@@ -42,18 +187,9 @@
     <t>Fly-MMU V1.0 H723</t>
   </si>
   <si>
-    <t>Fly-ProX10 H723</t>
-  </si>
-  <si>
     <t>Fly-Super5Pro H723</t>
   </si>
   <si>
-    <t>Fly-Super8Pro H743</t>
-  </si>
-  <si>
-    <t>Fly-Super8Pro H723</t>
-  </si>
-  <si>
     <t>Fysetc Spider King H723</t>
   </si>
   <si>
@@ -70,126 +206,6 @@
   </si>
   <si>
     <t>SKR3 EZ H743</t>
-  </si>
-  <si>
-    <t>BTT Kraken H723</t>
-  </si>
-  <si>
-    <t>BTT Octopus Pro v1.1 H723</t>
-  </si>
-  <si>
-    <t>BTT Scylla v1.0 H723</t>
-  </si>
-  <si>
-    <t>valkyrie  v2</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Requireed for V2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inputs </t>
-  </si>
-  <si>
-    <t>Humidity Sensor BME28</t>
-  </si>
-  <si>
-    <t>PT100/1000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thermisistors </t>
-  </si>
-  <si>
-    <t>steppers</t>
-  </si>
-  <si>
-    <t>Hot end Heater</t>
-  </si>
-  <si>
-    <t>12v PWM &gt;2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12V supply </t>
-  </si>
-  <si>
-    <t xml:space="preserve">24V supply </t>
-  </si>
-  <si>
-    <t>wifi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ethernet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PWM o/p Fans /SSR 1A </t>
-  </si>
-  <si>
-    <t>Output Digital</t>
-  </si>
-  <si>
-    <t>output 12V 2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cost $ with stepper drives </t>
-  </si>
-  <si>
-    <t>cost $ no drivers</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>drivers ea</t>
-  </si>
-  <si>
-    <t>6(2wire)2(4 wire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ruled out </t>
-  </si>
-  <si>
-    <t>no stock</t>
-  </si>
-  <si>
-    <t>1(bedout)</t>
-  </si>
-  <si>
-    <t>1option $13</t>
-  </si>
-  <si>
-    <t>1option$15 (E&amp;W)</t>
-  </si>
-  <si>
-    <t>10 (5,12,24v indipendant )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4(5A each) </t>
-  </si>
-  <si>
-    <t>TMC2240 $8</t>
-  </si>
-  <si>
-    <t>$88 (TMC2160)</t>
-  </si>
-  <si>
-    <t>$111(tmc2160)</t>
-  </si>
-  <si>
-    <t>6(2wire)2(4 wire) (5,12,24v indipendant )</t>
-  </si>
-  <si>
-    <t>4(6A)</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spoke to BTT no stock for a few weeks </t>
   </si>
 </sst>
 </file>
@@ -197,9 +213,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,7 +314,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3"/>
@@ -623,7 +639,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="4" customWidth="1"/>
@@ -645,75 +661,75 @@
     <col min="19" max="19" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
@@ -758,24 +774,24 @@
         <v>1</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" s="6" customFormat="1">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E5" s="7">
         <v>8</v>
@@ -815,15 +831,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" s="6" customFormat="1">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -842,24 +858,24 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" spans="1:19" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" s="13" customFormat="1">
       <c r="A7" s="11" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E7" s="12">
         <v>7</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -878,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="12">
         <v>1</v>
@@ -890,27 +906,27 @@
         <v>60</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="9" customFormat="1">
       <c r="A8" s="9" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E8" s="10">
         <v>8</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J8" s="10">
         <v>2</v>
@@ -928,24 +944,24 @@
         <v>1</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="9" customFormat="1">
       <c r="A9" s="14" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -964,12 +980,12 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
     </row>
-    <row r="10" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" s="6" customFormat="1">
       <c r="A10" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -988,18 +1004,18 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
     </row>
-    <row r="11" spans="1:19" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="18">
       <c r="A11" s="3"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19">
       <c r="B14" s="7"/>
       <c r="C14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1011,145 +1027,145 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1176,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
